--- a/gearbox-selector/IMAK-Reduktor-Formuller.xlsx
+++ b/gearbox-selector/IMAK-Reduktor-Formuller.xlsx
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Vinç kaldırma — direkt tambur</t>
+          <t>Vinç kaldırma (tambur + palanga)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Crane hoist — direct drum</t>
+          <t>Crane hoist (drum + falls)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Mᴛ = m·g·r ,  n = 9,55·v/r ,  Pm = Mᴛ·n/(9550·η)</t>
+          <t>Mᴛ = m·g·r/z ,  n = 9,55·v·z/r ,  Pm = Mᴛ·n/(9550·η)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Mᴛ = m·g·r ,  n = 9.55·v/r ,  Pm = Mᴛ·n/(9550·η)</t>
+          <t>Mᴛ = m·g·r/z ,  n = 9.55·v·z/r ,  Pm = Mᴛ·n/(9550·η)</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
@@ -2154,7 +2154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3134,12 +3134,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Vinç kaldırma — direkt tambur</t>
+          <t>Vinç kaldırma (tambur + palanga)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Crane hoist — direct drum</t>
+          <t>Crane hoist (drum + falls)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -3169,12 +3169,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Vinç kaldırma — direkt tambur</t>
+          <t>Vinç kaldırma (tambur + palanga)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Crane hoist — direct drum</t>
+          <t>Crane hoist (drum + falls)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3204,12 +3204,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Vinç kaldırma — direkt tambur</t>
+          <t>Vinç kaldırma (tambur + palanga)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Crane hoist — direct drum</t>
+          <t>Crane hoist (drum + falls)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -3239,36 +3239,32 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Palangalı kaldırma</t>
+          <t>Vinç kaldırma (tambur + palanga)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Pulley / block-and-tackle hoist</t>
+          <t>Crane hoist (drum + falls)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>z</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Kaldırılacak yük m</t>
+          <t>Palanga kat sayısı z</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Load m</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+          <t>Rope falls z</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="n">
-        <v>5000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3284,26 +3280,26 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Tambur çapı Ø</t>
+          <t>Kaldırılacak yük m</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Drum Ø</t>
+          <t>Load m</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="35">
@@ -3319,26 +3315,26 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Kaldırma hızı v</t>
+          <t>Tambur çapı Ø</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Lift speed v</t>
+          <t>Drum Ø</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>m/min</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36">
@@ -3354,22 +3350,26 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Palanga kat sayısı z</t>
+          <t>Kaldırma hızı v</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Rope falls z</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr"/>
+          <t>Lift speed v</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>m/min</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -3385,57 +3385,53 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>re</t>
+          <t>z</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Palanga verimi</t>
+          <t>Palanga kat sayısı z</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Reeving eff.</t>
+          <t>Rope falls z</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="n">
-        <v>0.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Yürütme (köprü/araba)</t>
+          <t>Palangalı kaldırma</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Travel (bridge / trolley)</t>
+          <t>Pulley / block-and-tackle hoist</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>re</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Yük Q</t>
+          <t>Palanga verimi</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Load Q</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+          <t>Reeving eff.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="n">
-        <v>5000</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="39">
@@ -3451,26 +3447,26 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Tekerlek çapı Ø</t>
+          <t>Yük Q</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Wheel Ø</t>
+          <t>Load Q</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="40">
@@ -3486,17 +3482,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Rulman çapı Ø</t>
+          <t>Tekerlek çapı Ø</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Bearing Ø</t>
+          <t>Wheel Ø</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3505,7 +3501,7 @@
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41">
@@ -3521,26 +3517,26 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>d</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Yürütme hızı v</t>
+          <t>Rulman çapı Ø</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Travel speed v</t>
+          <t>Bearing Ø</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
@@ -3556,22 +3552,26 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Yuvarlanma katsayısı f</t>
+          <t>Yürütme hızı v</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Rolling coeff. f</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr"/>
+          <t>Travel speed v</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
       <c r="G42" s="5" t="n">
-        <v>0.002</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43">
@@ -3587,57 +3587,53 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>mu</t>
+          <t>f</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Rulman sürtünmesi μ</t>
+          <t>Yuvarlanma katsayısı f</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Bearing friction μ</t>
+          <t>Rolling coeff. f</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Döner (slewing) tahrik</t>
+          <t>Yürütme (köprü/araba)</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Slewing drive</t>
+          <t>Travel (bridge / trolley)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mu</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Dönen kütle m</t>
+          <t>Rulman sürtünmesi μ</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Slewing mass m</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+          <t>Bearing friction μ</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="n">
-        <v>5000</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="45">
@@ -3653,26 +3649,26 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Kütle yarıçapı r</t>
+          <t>Dönen kütle m</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Mass radius r</t>
+          <t>Slewing mass m</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46">
@@ -3688,26 +3684,26 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>r</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Dönme devri</t>
+          <t>Kütle yarıçapı r</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Slew speed</t>
+          <t>Mass radius r</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3723,26 +3719,26 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Hızlanma süresi t</t>
+          <t>Dönme devri</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Accel time t</t>
+          <t>Slew speed</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="48">
@@ -3758,61 +3754,61 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Tf</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Sürtünme momenti Tf</t>
+          <t>Hızlanma süresi t</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Friction torque Tf</t>
+          <t>Accel time t</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Nm</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Asansör (halatlı)</t>
+          <t>Döner (slewing) tahrik</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Passenger lift (traction)</t>
+          <t>Slewing drive</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>Tf</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Kabin yükü Q</t>
+          <t>Sürtünme momenti Tf</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Car load Q</t>
+          <t>Friction torque Tf</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>Nm</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50">
@@ -3828,26 +3824,26 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Hız v</t>
+          <t>Kabin yükü Q</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Speed v</t>
+          <t>Car load Q</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="51">
@@ -3863,22 +3859,26 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>v</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Denge oranı b</t>
+          <t>Hız v</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Balance b</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
+          <t>Speed v</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
       <c r="G51" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3894,26 +3894,22 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Kasnak çapı Ø</t>
+          <t>Denge oranı b</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Sheave Ø</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+          <t>Balance b</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="n">
-        <v>600</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
@@ -3929,57 +3925,57 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Askı oranı (1/2)</t>
+          <t>Kasnak çapı Ø</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Roping factor (1/2)</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr"/>
+          <t>Sheave Ø</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Karıştırıcı — kanat yöntemi</t>
+          <t>Asansör (halatlı)</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Agitator — blade method</t>
+          <t>Passenger lift (traction)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Dd</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Pervane çapı Ød</t>
+          <t>Askı oranı (1/2)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Impeller Ø</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+          <t>Roping factor (1/2)</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="n">
-        <v>1500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3995,17 +3991,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Dd</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Pervane genişliği b</t>
+          <t>Pervane çapı Ød</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Blade width b</t>
+          <t>Impeller Ø</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -4014,7 +4010,7 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="56">
@@ -4030,17 +4026,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>k1</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>1. kanat sıvı yük. k₁</t>
+          <t>Pervane genişliği b</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Blade-1 liquid h. k₁</t>
+          <t>Blade width b</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>3500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -4065,17 +4061,17 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>k2</t>
+          <t>k1</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>2. kanat k₂</t>
+          <t>1. kanat sıvı yük. k₁</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Blade-2 k₂</t>
+          <t>Blade-1 liquid h. k₁</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -4084,7 +4080,7 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="58">
@@ -4100,17 +4096,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>k3</t>
+          <t>k2</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>3. kanat k₃</t>
+          <t>2. kanat k₂</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Blade-3 k₃</t>
+          <t>Blade-2 k₂</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -4119,7 +4115,7 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="59">
@@ -4135,26 +4131,26 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>k3</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Mil devri n</t>
+          <t>3. kanat k₃</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Shaft speed n</t>
+          <t>Blade-3 k₃</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>20</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="60">
@@ -4170,57 +4166,61 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Yoğunluk ρ</t>
+          <t>Mil devri n</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Density ρ</t>
+          <t>Shaft speed n</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>gr/cm³</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Karıştırıcı — güç sayısı (Np)</t>
+          <t>Karıştırıcı — kanat yöntemi</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Agitator — power number (Np)</t>
+          <t>Agitator — blade method</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Np</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Güç sayısı Np</t>
+          <t>Yoğunluk ρ</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Power number Np</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr"/>
+          <t>Density ρ</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>gr/cm³</t>
+        </is>
+      </c>
       <c r="G61" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="62">
@@ -4236,26 +4236,22 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>ro</t>
+          <t>Np</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Yoğunluk ρ</t>
+          <t>Güç sayısı Np</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Density ρ</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>kg/m³</t>
-        </is>
-      </c>
+          <t>Power number Np</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="63">
@@ -4271,26 +4267,26 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>ro</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Pervane çapı Ø</t>
+          <t>Yoğunluk ρ</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Impeller Ø</t>
+          <t>Density ρ</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg/m³</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="64">
@@ -4306,61 +4302,61 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Mil devri n</t>
+          <t>Pervane çapı Ø</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Shaft speed n</t>
+          <t>Impeller Ø</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Döner fırın / kurutma tamburu</t>
+          <t>Karıştırıcı — güç sayısı (Np)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Rotary kiln / drying drum</t>
+          <t>Agitator — power number (Np)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>İç çap Ø</t>
+          <t>Mil devri n</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Internal Ø</t>
+          <t>Shaft speed n</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>3000</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66">
@@ -4376,26 +4372,26 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Dönen yük m</t>
+          <t>İç çap Ø</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Rotating load m</t>
+          <t>Internal Ø</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>20000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="67">
@@ -4411,22 +4407,26 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Eksantriklik e</t>
+          <t>Dönen yük m</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Eccentricity e</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>Rotating load m</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="G67" s="3" t="n">
-        <v>0.35</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="68">
@@ -4442,26 +4442,22 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>e</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Dönme devri n</t>
+          <t>Eksantriklik e</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Rotation speed n</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>rpm</t>
-        </is>
-      </c>
+          <t>Eccentricity e</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="n">
-        <v>2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="69">
@@ -4477,61 +4473,61 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Sürtünme payı k</t>
+          <t>Dönme devri n</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Friction allow. k</t>
+          <t>Rotation speed n</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Ekstruder (vida)</t>
+          <t>Döner fırın / kurutma tamburu</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Extruder (screw)</t>
+          <t>Rotary kiln / drying drum</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>k</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Debi Q</t>
+          <t>Sürtünme payı k</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Throughput Q</t>
+          <t>Friction allow. k</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>kg/h</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
@@ -4547,26 +4543,26 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Özgül mek. enerji</t>
+          <t>Debi Q</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Specific mech. energy</t>
+          <t>Throughput Q</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>kg/h</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72">
@@ -4582,61 +4578,61 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>SME</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Vida devri n</t>
+          <t>Özgül mek. enerji</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Screw speed n</t>
+          <t>Specific mech. energy</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>kWh/kg</t>
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>100</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Valsli değirmen (un)</t>
+          <t>Ekstruder (vida)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Roller mill (flour)</t>
+          <t>Extruder (screw)</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Kapasite Q</t>
+          <t>Vida devri n</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Capacity Q</t>
+          <t>Screw speed n</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -4652,22 +4648,22 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Özgül enerji E</t>
+          <t>Kapasite Q</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Specific energy E</t>
+          <t>Capacity Q</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>kWh/t</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="G74" s="5" t="n">
@@ -4687,61 +4683,61 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Çıkış devri n</t>
+          <t>Özgül enerji E</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Output speed n</t>
+          <t>Specific energy E</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>kWh/t</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Çekiçli değirmen</t>
+          <t>Valsli değirmen (un)</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Hammer mill</t>
+          <t>Roller mill (flour)</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Kapasite Q</t>
+          <t>Çıkış devri n</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Capacity Q</t>
+          <t>Output speed n</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77">
@@ -4757,26 +4753,26 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Özgül enerji E</t>
+          <t>Kapasite Q</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Specific energy E</t>
+          <t>Capacity Q</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>kWh/t</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -4792,61 +4788,61 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Çıkış devri n</t>
+          <t>Özgül enerji E</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Output speed n</t>
+          <t>Specific energy E</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>kWh/t</t>
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1500</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Bilyalı değirmen (Bond)</t>
+          <t>Çekiçli değirmen</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Ball mill (Bond)</t>
+          <t>Hammer mill</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Kapasite Q</t>
+          <t>Çıkış devri n</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Capacity Q</t>
+          <t>Output speed n</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>20</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="80">
@@ -4862,26 +4858,26 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Wi</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>İş indeksi Wi</t>
+          <t>Kapasite Q</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Work index Wi</t>
+          <t>Capacity Q</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>kWh/t</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
@@ -4897,26 +4893,26 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Wi</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Besleme F₈₀</t>
+          <t>İş indeksi Wi</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Feed F₈₀</t>
+          <t>Work index Wi</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>µm</t>
+          <t>kWh/t</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>10000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -4932,17 +4928,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Pp</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Ürün P₈₀</t>
+          <t>Besleme F₈₀</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Product P₈₀</t>
+          <t>Feed F₈₀</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -4951,7 +4947,7 @@
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="83">
@@ -4967,61 +4963,61 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>Pp</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Değirmen devri n</t>
+          <t>Ürün P₈₀</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Mill speed n</t>
+          <t>Product P₈₀</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>µm</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Elek / plansifter</t>
+          <t>Bilyalı değirmen (Bond)</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Sifter / plansifter</t>
+          <t>Ball mill (Bond)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Salınan kütle m</t>
+          <t>Değirmen devri n</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Gyrating mass m</t>
+          <t>Mill speed n</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>300</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
@@ -5037,26 +5033,26 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Salınım yarıçapı r</t>
+          <t>Salınan kütle m</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Gyration throw r</t>
+          <t>Gyrating mass m</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86">
@@ -5072,26 +5068,26 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>r</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Devir n</t>
+          <t>Salınım yarıçapı r</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Speed n</t>
+          <t>Gyration throw r</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>220</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -5107,57 +5103,57 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Sönüm faktörü k</t>
+          <t>Devir n</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Damping factor k</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr"/>
+          <t>Speed n</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>rpm</t>
+        </is>
+      </c>
       <c r="G87" s="3" t="n">
-        <v>0.35</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Pelet değirmeni</t>
+          <t>Elek / plansifter</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Pellet mill</t>
+          <t>Sifter / plansifter</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>k</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Kapasite Q</t>
+          <t>Sönüm faktörü k</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Capacity Q</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>t/h</t>
-        </is>
-      </c>
+          <t>Damping factor k</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="5" t="n">
-        <v>8</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="89">
@@ -5173,26 +5169,26 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Özgül enerji E</t>
+          <t>Kapasite Q</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Specific energy E</t>
+          <t>Capacity Q</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>kWh/t</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -5208,61 +5204,61 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Çıkış devri n</t>
+          <t>Özgül enerji E</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Output speed n</t>
+          <t>Specific energy E</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>kWh/t</t>
         </is>
       </c>
       <c r="G90" s="5" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Kırıcı (taş / cevher)</t>
+          <t>Pelet değirmeni</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Crusher (stone / ore)</t>
+          <t>Pellet mill</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Kapasite Q</t>
+          <t>Çıkış devri n</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Capacity Q</t>
+          <t>Output speed n</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>t/h</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92">
@@ -5278,26 +5274,26 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Özgül enerji E</t>
+          <t>Kapasite Q</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Specific energy E</t>
+          <t>Capacity Q</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>kWh/t</t>
+          <t>t/h</t>
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -5313,61 +5309,61 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Çıkış devri n</t>
+          <t>Özgül enerji E</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Output speed n</t>
+          <t>Specific energy E</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>kWh/t</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Titreşimli elek</t>
+          <t>Kırıcı (taş / cevher)</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Vibrating screen</t>
+          <t>Crusher (stone / ore)</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Titreşen kütle m</t>
+          <t>Çıkış devri n</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Vibrating mass m</t>
+          <t>Output speed n</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95">
@@ -5383,26 +5379,26 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Genlik A</t>
+          <t>Titreşen kütle m</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Amplitude A</t>
+          <t>Vibrating mass m</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>5</v>
+        <v>800</v>
       </c>
     </row>
     <row r="96">
@@ -5418,26 +5414,26 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Ekssantrik devri</t>
+          <t>Genlik A</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Exciter speed</t>
+          <t>Amplitude A</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>900</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -5453,57 +5449,57 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Güç faktörü k</t>
+          <t>Ekssantrik devri</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Power factor k</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr"/>
+          <t>Exciter speed</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>rpm</t>
+        </is>
+      </c>
       <c r="G97" s="3" t="n">
-        <v>0.5</v>
+        <v>900</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Döner tabla / turntable</t>
+          <t>Titreşimli elek</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Rotary table / turntable</t>
+          <t>Vibrating screen</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>k</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Tabla + yük m</t>
+          <t>Güç faktörü k</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Table + load m</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+          <t>Power factor k</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
       <c r="G98" s="5" t="n">
-        <v>2000</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="99">
@@ -5519,26 +5515,26 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Yarıçap r</t>
+          <t>Tabla + yük m</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Radius r</t>
+          <t>Table + load m</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="100">
@@ -5554,26 +5550,26 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>r</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Çalışma devri n</t>
+          <t>Yarıçap r</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Operating speed n</t>
+          <t>Radius r</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>rpm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>5</v>
+        <v>800</v>
       </c>
     </row>
     <row r="101">
@@ -5589,26 +5585,26 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Hızlanma süresi t</t>
+          <t>Çalışma devri n</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Accel time t</t>
+          <t>Operating speed n</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -5624,61 +5620,61 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Tf</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Sürtünme momenti Tf</t>
+          <t>Hızlanma süresi t</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Friction torque Tf</t>
+          <t>Accel time t</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Nm</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Santrifüj pompa</t>
+          <t>Döner tabla / turntable</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Centrifugal pump</t>
+          <t>Rotary table / turntable</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>Tf</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Debi Q</t>
+          <t>Sürtünme momenti Tf</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Flow Q</t>
+          <t>Friction torque Tf</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>m³/h</t>
+          <t>Nm</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104">
@@ -5694,26 +5690,26 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Basma yüksekliği H</t>
+          <t>Debi Q</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Head H</t>
+          <t>Flow Q</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³/h</t>
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105">
@@ -5729,22 +5725,26 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Özgül ağırlık SG</t>
+          <t>Basma yüksekliği H</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Specific gravity SG</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr"/>
+          <t>Head H</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="G105" s="3" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
@@ -5760,22 +5760,22 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>pe</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Pompa verimi ηp</t>
+          <t>Özgül ağırlık SG</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Pump eff. ηp</t>
+          <t>Specific gravity SG</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -5791,61 +5791,57 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>pe</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Pompa devri n</t>
+          <t>Pompa verimi ηp</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Pump speed n</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>rpm</t>
-        </is>
-      </c>
+          <t>Pump eff. ηp</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr"/>
       <c r="G107" s="3" t="n">
-        <v>1450</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Pistonlu / pozitif deplasmanlı pompa</t>
+          <t>Santrifüj pompa</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Reciprocating / PD pump</t>
+          <t>Centrifugal pump</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Debi Q</t>
+          <t>Pompa devri n</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Flow Q</t>
+          <t>Pump speed n</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>m³/h</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>20</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="109">
@@ -5861,26 +5857,26 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Basma yüksekliği H</t>
+          <t>Debi Q</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Head H</t>
+          <t>Flow Q</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³/h</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110">
@@ -5896,22 +5892,26 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Özgül ağırlık SG</t>
+          <t>Basma yüksekliği H</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Specific gravity SG</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr"/>
+          <t>Head H</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="G110" s="5" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111">
@@ -5927,22 +5927,22 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>pe</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Pompa verimi ηp</t>
+          <t>Özgül ağırlık SG</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Pump eff. ηp</t>
+          <t>Specific gravity SG</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr"/>
       <c r="G111" s="3" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -5958,61 +5958,57 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>pe</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Pompa devri n</t>
+          <t>Pompa verimi ηp</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Pump speed n</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>rpm</t>
-        </is>
-      </c>
+          <t>Pump eff. ηp</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr"/>
       <c r="G112" s="5" t="n">
-        <v>300</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Santrifüj fan / körük</t>
+          <t>Pistonlu / pozitif deplasmanlı pompa</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Centrifugal fan / blower</t>
+          <t>Reciprocating / PD pump</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Hava debisi Q</t>
+          <t>Pompa devri n</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Air flow Q</t>
+          <t>Pump speed n</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>m³/h</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>5000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114">
@@ -6028,26 +6024,26 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>dp</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Basınç artışı Δp</t>
+          <t>Hava debisi Q</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Pressure rise Δp</t>
+          <t>Air flow Q</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m³/h</t>
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="115">
@@ -6063,22 +6059,26 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>fe</t>
+          <t>dp</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Fan verimi ηf</t>
+          <t>Basınç artışı Δp</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Fan eff. ηf</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr"/>
+          <t>Pressure rise Δp</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="G115" s="3" t="n">
-        <v>0.65</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="116">
@@ -6094,25 +6094,56 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
+          <t>fe</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Fan verimi ηf</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Fan eff. ηf</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Santrifüj fan / körük</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Centrifugal fan / blower</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
           <t>n</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Fan devri n</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>Fan speed n</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>rpm</t>
         </is>
       </c>
-      <c r="G116" s="5" t="n">
+      <c r="G117" s="3" t="n">
         <v>1450</v>
       </c>
     </row>
@@ -6130,7 +6161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6823,12 +6854,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Vinç kaldırma — direkt tambur</t>
+          <t>Vinç kaldırma (tambur + palanga)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Crane hoist — direct drum</t>
+          <t>Crane hoist (drum + falls)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -6860,114 +6891,110 @@
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Tambur momenti</t>
+          <t>Palanga kat sayısı</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Drum moment</t>
+          <t>Rope falls</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Mᴛ = 2000·9,81·0.15</t>
+          <t>z</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2943</v>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Nm</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>Tambur momenti</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Drum moment</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Mᴛ = 2000·9,81·0.15/1</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2943</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
           <t>Tambur devri</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Drum speed</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>n = 9,55·0.167/0.15</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>n = 9,55·0.167·1/0.15</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>10.6</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>d/dk</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Palangalı kaldırma</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Pulley / block-and-tackle hoist</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Tambur yarıçapı</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Drum radius</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>r = 400/2000</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="3" t="inlineStr"/>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Tambur momenti</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Drum moment</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Mᴛ = 5000·9,81·0.2/(2·0.95)</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>5163.16</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Nm</t>
         </is>
       </c>
     </row>
@@ -6976,149 +7003,149 @@
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
+          <t>Tambur momenti</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Drum moment</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Mᴛ = 5000·9,81·0.2/(2·0.95)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5163.16</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
           <t>Tambur devri</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Drum speed</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>n = 9,55·0.133·2/0.2</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F31" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>d/dk</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Yürütme (köprü/araba)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Travel (bridge / trolley)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Tekerlek momenti</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Wheel moment</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Mᴛ = [5000·0.002+0.008·5000·0.05]·9,81</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F32" s="5" t="n">
         <v>117.72</v>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Tekerlek devri</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Wheel speed</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>n = 60000·1.5/(π·500)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F33" s="3" t="n">
         <v>57.3</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>d/dk</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Döner (slewing) tahrik</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Slewing drive</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Atalet momenti</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Inertia</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>J = 5000·3²</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F34" s="5" t="n">
         <v>45000</v>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>kg·m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Açısal ivme</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Ang. accel</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>α = (2π·1.5/60)/5</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>rad/s²</t>
         </is>
       </c>
     </row>
@@ -7127,87 +7154,87 @@
       <c r="B35" s="3" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
+          <t>Açısal ivme</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ang. accel</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>α = (2π·1.5/60)/5</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>rad/s²</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Mᴛ = 45000·0.031+500</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F36" s="5" t="n">
         <v>1913.72</v>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Asansör (halatlı)</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Passenger lift (traction)</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Dengesiz kuvvet</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Out-of-balance force</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>F = 1000·(1−0.5)·9,81</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F37" s="3" t="n">
         <v>4905</v>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="3" t="inlineStr"/>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Çıkış gücü</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Output power</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Pₒ = 4905·1/1000</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>kW</t>
         </is>
       </c>
     </row>
@@ -7216,83 +7243,83 @@
       <c r="B38" s="5" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
+          <t>Çıkış gücü</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Output power</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Pₒ = 4905·1/1000</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
           <t>Kasnak devri</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Sheave speed</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>n = 60·1·1/(π·0.6)</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F39" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>d/dk</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Karıştırıcı — kanat yöntemi</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Agitator — blade method</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>1. kanat momenti</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Blade-1 moment</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>M₁ = 0.75·0.1·3.5·1100·10</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F40" s="5" t="n">
         <v>2887.5</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>2. kanat momenti</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Blade-2 moment</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>M₂</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>2062.5</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -7305,21 +7332,21 @@
       <c r="B41" s="3" t="inlineStr"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>3. kanat momenti</t>
+          <t>2. kanat momenti</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Blade-3 moment</t>
+          <t>Blade-2 moment</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>M₃</t>
+          <t>M₂</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1237.5</v>
+        <v>2062.5</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -7332,87 +7359,87 @@
       <c r="B42" s="5" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
+          <t>3. kanat momenti</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Blade-3 moment</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>M₃</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1237.5</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
           <t>Toplam moment</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Total moment</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 2887.5+2062.5+1237.5</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F43" s="3" t="n">
         <v>6187.5</v>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Karıştırıcı — güç sayısı (Np)</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Agitator — power number (Np)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Devir (1/s)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Rev/s</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>N = 60/60</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F44" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>1/s</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr"/>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Çıkış gücü</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Output power</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Pₒ = 1.5·1000·1³·0.5⁵/1000</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>kW</t>
         </is>
       </c>
     </row>
@@ -7421,56 +7448,48 @@
       <c r="B45" s="3" t="inlineStr"/>
       <c r="C45" s="3" t="inlineStr">
         <is>
+          <t>Çıkış gücü</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Output power</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Pₒ = 1.5·1000·1³·0.5⁵/1000</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·0.05/60</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F46" s="5" t="n">
         <v>7.46</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Nm</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Döner fırın / kurutma tamburu</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Rotary kiln / drying drum</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Çıkış momenti</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Output moment</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Mᴛ = 1.2·20000·9,81·1.5·0.35</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>123606</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -7481,248 +7500,256 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>Döner fırın / kurutma tamburu</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Rotary kiln / drying drum</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Çıkış momenti</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Output moment</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Mᴛ = 1.2·20000·9,81·1.5·0.35</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>123606</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>Ekstruder (vida)</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Extruder (screw)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 0.2·200</t>
         </is>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F48" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr"/>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·40/100</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F49" s="3" t="n">
         <v>3820</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Valsli değirmen (un)</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Roller mill (flour)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 10·10</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F50" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr"/>
-      <c r="C50" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·100/300</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F51" s="3" t="n">
         <v>3183.33</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Çekiçli değirmen</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Hammer mill</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 15·5</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F52" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr"/>
-      <c r="C52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·75/1500</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F53" s="3" t="n">
         <v>477.5</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Bilyalı değirmen (Bond)</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Ball mill (Bond)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Özgül enerji (Bond)</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Specific energy (Bond)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>E = 10·13·(1/√100−1/√10000)</t>
         </is>
       </c>
-      <c r="F53" s="3" t="n">
+      <c r="F54" s="5" t="n">
         <v>11.7</v>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>kWh/t</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr"/>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Çıkış gücü</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Output power</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Pₒ = 11.7·20</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>234</v>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>kW</t>
         </is>
       </c>
     </row>
@@ -7731,87 +7758,87 @@
       <c r="B55" s="3" t="inlineStr"/>
       <c r="C55" s="3" t="inlineStr">
         <is>
+          <t>Çıkış gücü</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Output power</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Pₒ = 11.7·20</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="5" t="inlineStr"/>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·234/18</t>
         </is>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F56" s="5" t="n">
         <v>124150</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Elek / plansifter</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Sifter / plansifter</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Açısal hız</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Angular speed</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>ω = 2π·220/60</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F57" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>rad/s</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr"/>
-      <c r="B57" s="3" t="inlineStr"/>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Çıkış gücü</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Output power</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Pₒ = 0.35·300·0.04²·23³/1000</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>kW</t>
         </is>
       </c>
     </row>
@@ -7820,211 +7847,211 @@
       <c r="B58" s="5" t="inlineStr"/>
       <c r="C58" s="5" t="inlineStr">
         <is>
+          <t>Çıkış gücü</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Output power</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Pₒ = 0.35·300·0.04²·23³/1000</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·2.05/220</t>
         </is>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F59" s="3" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Pelet değirmeni</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Pellet mill</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 45·8</t>
         </is>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F60" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·360/250</t>
         </is>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F61" s="3" t="n">
         <v>13752</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Kırıcı (taş / cevher)</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Crusher (stone / ore)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 2·50</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="F62" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="3" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·100/200</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F63" s="3" t="n">
         <v>4775</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Titreşimli elek</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Vibrating screen</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Açısal hız</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Angular speed</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>ω = 2π·900/60</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="F64" s="5" t="n">
         <v>94.2</v>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>rad/s</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr"/>
-      <c r="B64" s="5" t="inlineStr"/>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Çıkış gücü</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Output power</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Pₒ = 0.5·800·0.005²·94.2³/1000</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>kW</t>
         </is>
       </c>
     </row>
@@ -8033,87 +8060,87 @@
       <c r="B65" s="3" t="inlineStr"/>
       <c r="C65" s="3" t="inlineStr">
         <is>
+          <t>Çıkış gücü</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Output power</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Pₒ = 0.5·800·0.005²·94.2³/1000</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr"/>
+      <c r="B66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·8.37/900</t>
         </is>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F66" s="5" t="n">
         <v>88.83</v>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Döner tabla / turntable</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Rotary table / turntable</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Atalet momenti</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Inertia</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>J = 0,5·2000·0.8²</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F67" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>kg·m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr"/>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Açısal ivme</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Ang. accel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>α = (2π·5/60)/3</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>rad/s²</t>
         </is>
       </c>
     </row>
@@ -8122,209 +8149,236 @@
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
+          <t>Açısal ivme</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Ang. accel</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>α = (2π·5/60)/3</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>rad/s²</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 640·0.175+200</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F69" s="3" t="n">
         <v>311.7</v>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Santrifüj pompa</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Centrifugal pump</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 50·30·1/(367·0.7)</t>
         </is>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F70" s="5" t="n">
         <v>5.84</v>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr"/>
-      <c r="B70" s="5" t="inlineStr"/>
-      <c r="C70" s="5" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·5.84/1450</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F71" s="3" t="n">
         <v>38.46</v>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Pistonlu / pozitif deplasmanlı pompa</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Reciprocating / PD pump</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Pₒ = 20·60·1/(367·0.85)</t>
         </is>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="F72" s="5" t="n">
         <v>3.85</v>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr"/>
-      <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr"/>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·3.85/300</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F73" s="3" t="n">
         <v>122.46</v>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>Santrifüj fan / körük</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Centrifugal fan / blower</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Çıkış gücü</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Output power</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>Pₒ = (5000/3600)·1000/(1000·0.65)</t>
         </is>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F74" s="5" t="n">
         <v>2.14</v>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>kW</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr"/>
-      <c r="B74" s="5" t="inlineStr"/>
-      <c r="C74" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Çıkış momenti</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Output moment</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Mᴛ = 9550·2.14/1450</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F75" s="3" t="n">
         <v>14.07</v>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Nm</t>
         </is>
